--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>687.</t>
+          <t>736.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2003.</t>
+          <t>2017.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>910.</t>
+          <t>959.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>31.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>165.</t>
+          <t>175.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2380.</t>
+          <t>2394.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5198.</t>
+          <t>5322.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>669.</t>
+          <t>679.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>752.</t>
+          <t>756.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>142.</t>
+          <t>164.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2237.</t>
+          <t>2354.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>372.</t>
+          <t>390.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5094.</t>
+          <t>5218.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>243.</t>
+          <t>250.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1656.</t>
+          <t>1786.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3848.</t>
+          <t>3976.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4070.</t>
+          <t>4197.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4094.</t>
+          <t>4221.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5248.</t>
+          <t>5372.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2700.</t>
+          <t>2829.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1392.</t>
+          <t>1406.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>736.</t>
+          <t>881.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2017.</t>
+          <t>1914.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>959.</t>
+          <t>1104.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>31.</t>
+          <t>64.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>175.</t>
+          <t>261.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2394.</t>
+          <t>2215.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5322.</t>
+          <t>137.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,53 +892,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>679.</t>
+          <t>5474.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>59782330</v>
+        <v>10000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>756.</t>
+          <t>714.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08-Jun-2026 11:00 AM</t>
+          <t>08-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18-Jun-2026 05:00 PM</t>
+          <t>18-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -978,25 +978,25 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3,87,50,583</t>
+          <t>5,97,82,330</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>38750583</v>
+        <v>59782330</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1016,45 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>164.</t>
+          <t>773.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>08-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>18-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>PWD</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>3,87,50,583</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31803649</v>
+        <v>38750583</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1074,45 +1074,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2354.</t>
+          <t>244.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>27053943</v>
+        <v>31803649</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1132,103 +1132,103 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>390.</t>
+          <t>2722.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>30-May-2026 01:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>19-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>20-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>2,70,53,943</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16751919</v>
+        <v>27053943</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5218.</t>
+          <t>608.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13450000</v>
+        <v>16751919</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1248,45 +1248,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>250.</t>
+          <t>5375.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08-Jun-2026 09:00 AM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15-Jun-2026 02:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Construction of Chief Engineer (Distribution) Garhwal Zone, Office Building and Other Misc. Civil Works at 18 E.C. Road, UPCL Campus, Dehradun.] [ECC-17/2026-27][2026_UPCL8_96394_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MD - UPCL||CE (Civil)||SE (Civil)</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1,20,79,891</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>12079891</v>
+        <v>13450000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SnkkmSbr53KLUrrNIrRVrNQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1786.</t>
+          <t>2370.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3976.</t>
+          <t>4404.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4197.</t>
+          <t>4566.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4221.</t>
+          <t>4577.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5372.</t>
+          <t>5517.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2829.</t>
+          <t>3378.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1406.</t>
+          <t>1375.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>881.</t>
+          <t>1113.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1914.</t>
+          <t>1974.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1104.</t>
+          <t>1322.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>64.</t>
+          <t>95.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>261.</t>
+          <t>378.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2215.</t>
+          <t>196.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>15861542</v>
+        <v>11000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,53 +834,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>137.</t>
+          <t>810.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>08-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>18-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>5,97,82,330</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11000000</v>
+        <v>59782330</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,53 +892,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5474.</t>
+          <t>853.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>08-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>18-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>19-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>PWD</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>3,87,50,583</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10000000</v>
+        <v>38750583</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,45 +958,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>714.</t>
+          <t>661.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>59782330</v>
+        <v>34440000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1016,45 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>773.</t>
+          <t>195.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08-Jun-2026 11:00 AM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,87,50,583</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>38750583</v>
+        <v>31984321</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>244.</t>
+          <t>364.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2722.</t>
+          <t>2637.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>608.</t>
+          <t>655.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1240,457 +1240,51 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5375.</t>
+          <t>1488.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,30,03,957</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>13450000</v>
+        <v>13003957</v>
       </c>
       <c r="L15" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2370.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>10-Jun-2026 04:50 PM</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>03-Jul-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Medical and Health</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4404.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 05:05 PM</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4566.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 10:00 AM</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4577.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>04-Jun-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>23-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5517.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>08-May-2026 09:00 AM</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>18-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>19-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5,00,00,000</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>50000000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>3378.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Central eProcure</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1375.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>03-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:05 PM</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1,30,03,957</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>13003957</v>
-      </c>
-      <c r="L22" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1113.</t>
+          <t>1424.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1974.</t>
+          <t>2124.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1322.</t>
+          <t>1616.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>95.</t>
+          <t>129.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>378.</t>
+          <t>494.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>196.</t>
+          <t>2394.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>11000000</v>
+        <v>15861542</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,53 +834,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>810.</t>
+          <t>328.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08-Jun-2026 05:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18-Jun-2026 04:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2661-70][2026_HIMUD_136074_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5,97,82,330</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>59782330</v>
+        <v>11000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScApFqJ1FmWb2jrLcGPS58w%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>853.</t>
+          <t>905.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>661.</t>
+          <t>1332.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>195.</t>
+          <t>514.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>364.</t>
+          <t>548.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2637.</t>
+          <t>2671.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>655.</t>
+          <t>781.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1488.</t>
+          <t>1605.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1424.</t>
+          <t>288.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11-Jun-2026 12:30 PM</t>
+          <t>18-Jun-2026 10:45 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 05:00 PM</t>
+          <t>06-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02-Jul-2026 11:00 AM</t>
+          <t>07-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
+          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15,39,73,912</t>
+          <t>19,08,13,426</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>153973912</v>
+        <v>190813426</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -548,49 +548,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2124.</t>
+          <t>1578.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02-Jun-2026 11:00 AM</t>
+          <t>11-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17-Jun-2026 05:00 PM</t>
+          <t>01-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:00 PM</t>
+          <t>02-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
+          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9,61,59,224</t>
+          <t>15,39,73,912</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>96159224</v>
+        <v>153973912</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1616.</t>
+          <t>1898.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>02-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:00 PM</t>
+          <t>01-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:10 PM</t>
+          <t>02-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of school building in GSSS Dhareru] [20263F49E116 A6A8 4850 98F9 76FBCFD64BD91026SSP][2026_HBC_528054_1]</t>
+          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||HSSPP Panchkula</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,73,65,727</t>
+          <t>9,61,59,224</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17365727</v>
+        <v>96159224</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJD%2FD2%2FEIE7Rtc6PfuAfdHA%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>129.</t>
+          <t>631.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>12-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>23-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>HP SIDC Limited</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>2,79,52,391</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>29140100</v>
+        <v>27952391</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -726,45 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>494.</t>
+          <t>2096.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>27952391</v>
+        <v>15861542</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2394.</t>
+          <t>698.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>15861542</v>
+        <v>11000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>328.</t>
+          <t>5771.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>905.</t>
+          <t>2555.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08-Jun-2026 11:00 AM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18-Jun-2026 05:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19-Jun-2026 11:00 AM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of Library building at Rehan Tehsil Fatehpur Distt. Kangra HP ] [1925-75 Dated 01-06-2026][2026_PWD_135736_1]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>PWD</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3,87,50,583</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>38750583</v>
+        <v>34440000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScktuyPwMwhvUC14n%2F2dCVg%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1332.</t>
+          <t>926.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -968,35 +968,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>34440000</v>
+        <v>31984321</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1016,45 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>514.</t>
+          <t>933.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31984321</v>
+        <v>31803649</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1074,45 +1074,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>548.</t>
+          <t>3055.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>30-May-2026 01:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>19-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>20-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>2,70,53,943</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>31803649</v>
+        <v>27053943</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1132,103 +1132,103 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2671.</t>
+          <t>1091.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>27053943</v>
+        <v>16751919</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>781.</t>
+          <t>5692.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16751919</v>
+        <v>13450000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1248,43 +1248,391 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1605.</t>
+          <t>4589.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>10-Jun-2026 04:50 PM</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Medical and Health</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5346.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 05:05 PM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5385.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5391.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>04-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5801.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>08-May-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5142.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>08-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4,48,00,000</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Central eProcure</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1807.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>1,30,03,957</t>
         </is>
       </c>
-      <c r="K15" t="n">
+      <c r="K21" t="n">
         <v>13003957</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>288.</t>
+          <t>299.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1578.</t>
+          <t>1586.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1898.</t>
+          <t>1902.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>631.</t>
+          <t>244.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>2,91,40,100</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>27952391</v>
+        <v>29140100</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -726,45 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2096.</t>
+          <t>636.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>12-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>23-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>HP SIDC Limited</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>2,79,52,391</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>15861542</v>
+        <v>27952391</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>698.</t>
+          <t>2100.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>11000000</v>
+        <v>15861542</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5771.</t>
+          <t>714.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -896,49 +896,49 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2555.</t>
+          <t>5785.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>34440000</v>
+        <v>10000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>926.</t>
+          <t>2594.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -968,35 +968,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>19-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>22-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>3,44,40,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>31984321</v>
+        <v>34440000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1016,45 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>933.</t>
+          <t>937.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31803649</v>
+        <v>31984321</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1074,45 +1074,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3055.</t>
+          <t>940.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>27053943</v>
+        <v>31803649</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1132,103 +1132,103 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1091.</t>
+          <t>3078.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>30-May-2026 01:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>19-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>20-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>2,70,53,943</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16751919</v>
+        <v>27053943</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5692.</t>
+          <t>1108.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13450000</v>
+        <v>16751919</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1244,49 +1244,49 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4589.</t>
+          <t>5708.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>50000000</v>
+        <v>13450000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1306,32 +1306,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5346.</t>
+          <t>4623.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1364,27 +1364,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5385.</t>
+          <t>5371.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5391.</t>
+          <t>5410.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>04-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5801.</t>
+          <t>5416.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>04-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>23-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1538,27 +1538,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5142.</t>
+          <t>5815.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08-Jun-2026 04:00 PM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1568,15 +1568,15 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4,48,00,000</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>44800000</v>
+        <v>50000000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1596,43 +1596,101 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1807.</t>
+          <t>5171.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>08-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4,48,00,000</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Central eProcure</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1812.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>1,30,03,957</t>
         </is>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>13003957</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>299.</t>
+          <t>630.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1586.</t>
+          <t>1814.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1902.</t>
+          <t>2104.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>244.</t>
+          <t>265.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>636.</t>
+          <t>702.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2100.</t>
+          <t>2296.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>714.</t>
+          <t>882.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5785.</t>
+          <t>5986.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2594.</t>
+          <t>1268.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -968,35 +968,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>19-Jun-2026 06:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22-Jun-2026 11:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Community Hall and various work In Galana village] [02/2026-27 (35)][2026_UITKo_568255_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>UIT Kota||Addl. C.E.||S.E. - II||Ex.En. - I</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3,44,40,000</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>34440000</v>
+        <v>31984321</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0ZlAjilMxUeiMh1GVzwoRQ%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1016,45 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>937.</t>
+          <t>1108.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31984321</v>
+        <v>31803649</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1074,161 +1074,161 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>940.</t>
+          <t>1248.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>31803649</v>
+        <v>16751919</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3078.</t>
+          <t>5906.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30-May-2026 01:00 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19-Jun-2026 03:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20-Jun-2026 03:00 PM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[Construction of School for Divyang Children at Chaitanya Aashram, Jammu] [e-NIT No. CO/Proj./187/324 DT 30.05.2026][2026_SMVSB_311201_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SHRI MATA VAISHNO DEVI SHRINE BOARD</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2,70,53,943</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>27053943</v>
+        <v>13450000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6HRkjgWF8V3Jgv%2Ftf7dwQg%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1108.</t>
+          <t>4964.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>16751919</v>
+        <v>50000000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1244,49 +1244,49 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5708.</t>
+          <t>5586.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>13450000</v>
+        <v>50000000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1306,32 +1306,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4623.</t>
+          <t>5613.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>04-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>23-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1364,27 +1364,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5371.</t>
+          <t>5619.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>04-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>23-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1422,27 +1422,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5410.</t>
+          <t>6015.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5416.</t>
+          <t>5401.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>08-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>29-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1510,15 +1510,15 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>4,48,00,000</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>50000000</v>
+        <v>44800000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1538,159 +1538,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5815.</t>
+          <t>1964.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,30,03,957</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>50000000</v>
+        <v>13003957</v>
       </c>
       <c r="L20" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>5171.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Central eProcure</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>10</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1812.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>03-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:05 PM</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>1,30,03,957</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>13003957</v>
-      </c>
-      <c r="L22" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>630.</t>
+          <t>635.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1814.</t>
+          <t>1795.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2104.</t>
+          <t>2085.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>702.</t>
+          <t>703.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2296.</t>
+          <t>2277.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>882.</t>
+          <t>886.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5986.</t>
+          <t>6018.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1268.</t>
+          <t>1273.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1108.</t>
+          <t>1110.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1248.</t>
+          <t>1252.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5906.</t>
+          <t>5938.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4964.</t>
+          <t>4996.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5586.</t>
+          <t>5618.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5613.</t>
+          <t>5645.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5619.</t>
+          <t>5651.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6015.</t>
+          <t>6047.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5401.</t>
+          <t>5433.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1964.</t>
+          <t>1966.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>635.</t>
+          <t>783.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1795.</t>
+          <t>1854.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2085.</t>
+          <t>2128.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>265.</t>
+          <t>312.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>703.</t>
+          <t>806.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2277.</t>
+          <t>2315.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>886.</t>
+          <t>942.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6018.</t>
+          <t>6162.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1273.</t>
+          <t>1401.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1110.</t>
+          <t>1228.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1252.</t>
+          <t>1293.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5938.</t>
+          <t>6082.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4996.</t>
+          <t>5317.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5618.</t>
+          <t>5809.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5645.</t>
+          <t>5836.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5651.</t>
+          <t>5842.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6047.</t>
+          <t>6191.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5433.</t>
+          <t>5679.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1966.</t>
+          <t>2037.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>783.</t>
+          <t>1017.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1854.</t>
+          <t>1794.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2128.</t>
+          <t>1994.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>312.</t>
+          <t>45.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>15-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>16-Jul-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>9,55,97,065</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>29140100</v>
+        <v>95597065</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -726,45 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>806.</t>
+          <t>8.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12-Jun-2026 11:00 AM</t>
+          <t>22-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>06-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>23-Jun-2026 11:00 AM</t>
+          <t>06-Jul-2026 03:30 PM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of RTO Office Building at Nahan, Distt. Sirmour (HP).] [Job No. 4][2026_SIDC_136318_1]</t>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>HP SIDC Limited</t>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2,79,52,391</t>
+          <t>4,50,46,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>27952391</v>
+        <v>45046000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SaPZgiL2NlyjRgJ5H4WKunw%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2315.</t>
+          <t>333.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>2,91,40,100</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>15861542</v>
+        <v>29140100</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -842,45 +842,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>942.</t>
+          <t>2160.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11000000</v>
+        <v>15861542</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -900,45 +900,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6162.</t>
+          <t>1004.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>10000000</v>
+        <v>11000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -950,53 +950,53 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1401.</t>
+          <t>5975.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>31984321</v>
+        <v>10000000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1016,45 +1016,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1228.</t>
+          <t>1516.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>15-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>3,19,84,321</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31803649</v>
+        <v>31984321</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Central eProcure</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1074,103 +1074,103 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1293.</t>
+          <t>1285.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>12-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 11:30 AM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>3,18,03,649</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>16751919</v>
+        <v>31803649</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6082.</t>
+          <t>1230.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>1,67,51,919</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>13450000</v>
+        <v>16751919</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1186,49 +1186,49 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5317.</t>
+          <t>5898.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>23-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>25-Jun-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>50000000</v>
+        <v>13450000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1248,32 +1248,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5809.</t>
+          <t>5220.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1306,27 +1306,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5836.</t>
+          <t>5656.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5842.</t>
+          <t>5682.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>04-Jun-2026 10:00 AM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1422,27 +1422,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6191.</t>
+          <t>5688.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>04-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>23-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>24-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5679.</t>
+          <t>6003.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08-Jun-2026 04:00 PM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1510,15 +1510,15 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4,48,00,000</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>44800000</v>
+        <v>50000000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1538,43 +1538,101 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2037.</t>
+          <t>5538.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>08-Jun-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4,48,00,000</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>44800000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Central eProcure</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2010.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>03-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>24-Jun-2026 06:00 PM</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>25-Jun-2026 06:05 PM</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>1,30,03,957</t>
         </is>
       </c>
-      <c r="K20" t="n">
+      <c r="K21" t="n">
         <v>13003957</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1017.</t>
+          <t>1138.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1794.</t>
+          <t>1795.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1994.</t>
+          <t>1989.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.</t>
+          <t>167.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>24.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>333.</t>
+          <t>348.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2160.</t>
+          <t>2151.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1004.</t>
+          <t>1037.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5975.</t>
+          <t>5612.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1516.</t>
+          <t>1574.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1285.</t>
+          <t>1367.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1230.</t>
+          <t>1256.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5898.</t>
+          <t>5552.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5220.</t>
+          <t>5059.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5656.</t>
+          <t>5375.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5682.</t>
+          <t>5389.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5688.</t>
+          <t>5395.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>6003.</t>
+          <t>5641.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5538.</t>
+          <t>5286.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2010.</t>
+          <t>2078.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,174 +481,174 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Best Tender</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1138.</t>
+          <t>134.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-Jun-2026 10:45 AM</t>
+          <t>22-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06-Jul-2026 05:00 PM</t>
+          <t>06-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>07-Jul-2026 03:00 PM</t>
+          <t>06-Jul-2026 03:30 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>19,08,13,426</t>
+          <t>4,50,46,000</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>190813426</v>
+        <v>45046000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Best Tender</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1795.</t>
+          <t>420.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11-Jun-2026 12:30 PM</t>
+          <t>12-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>01-Jul-2026 05:00 PM</t>
+          <t>30-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02-Jul-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
+          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
+          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15,39,73,912</t>
+          <t>2,91,40,100</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>153973912</v>
+        <v>29140100</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Best Tender</t>
+          <t>Review Tender</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1989.</t>
+          <t>328.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02-Jun-2026 11:00 AM</t>
+          <t>25-Jun-2026 03:15 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>01-Jul-2026 05:00 PM</t>
+          <t>14-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>02-Jul-2026 03:00 PM</t>
+          <t>15-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
+          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9,61,59,224</t>
+          <t>2,81,43,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>96159224</v>
+        <v>28143000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -668,45 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>167.</t>
+          <t>82.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22-Jun-2026 05:00 PM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>15-Jul-2026 05:00 PM</t>
+          <t>03-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>16-Jul-2026 09:00 AM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
+          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9,55,97,065</t>
+          <t>1,59,20,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>95597065</v>
+        <v>15920000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Punjab eProcurement</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -726,45 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>1325.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22-Jun-2026 04:15 PM</t>
+          <t>15-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:00 PM</t>
+          <t>29-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:30 PM</t>
+          <t>30-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4,50,46,000</t>
+          <t>1,10,00,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>45046000</v>
+        <v>11000000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -784,45 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>348.</t>
+          <t>4863.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>14-May-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>1,00,00,000</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29140100</v>
+        <v>10000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -834,53 +834,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Haryana eTenders</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2151.</t>
+          <t>193.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>01-May-2026 03:00 PM</t>
+          <t>25-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>17-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26-Jun-2026 11:00 AM</t>
+          <t>18-Jul-2026 12:00 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Haryana Government||GJUS and T Hisar</t>
+          <t>PWD||CE RandB Jammu</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1,58,61,542</t>
+          <t>8,46,91,000</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>15861542</v>
+        <v>84691000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -892,53 +892,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Himachal eTenders</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1037.</t>
+          <t>377.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>23-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>03-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>04-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>6,07,83,682</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>11000000</v>
+        <v>60783682</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -954,56 +954,56 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>5612.</t>
+          <t>683.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>25-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25-Jun-2026 04:00 PM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1,00,00,000</t>
+          <t>1,39,27,000</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10000000</v>
+        <v>13927000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1012,165 +1012,165 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1574.</t>
+          <t>158.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-Jun-2026 05:00 PM</t>
+          <t>25-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 05:00 PM</t>
+          <t>02-Jul-2026 12:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>02-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[Construction of Library in ...] [2026125F74B7 AD39 48A3 A12F 6DE8C0F8C500345ULB][2026_HRY_529347_1]</t>
+          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Haryana Government||Urban Local Bodies||MC Barwala</t>
+          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3,19,84,321</t>
+          <t>1,98,80,991</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>31984321</v>
+        <v>19880991</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SA2Kjj28gTwLxF2UEZTLzsw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Central eProcure</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1367.</t>
+          <t>4807.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:00 PM</t>
+          <t>21-May-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:30 AM</t>
+          <t>03-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF QUARTER GUARD BUILDING AT BSF CAMPUS BOI, DISTT. KANGRA OF 185 BN BSF (NOW 24 BN BSF) UNDER SHQ BSF GSP] [10/HQSDGWC/Engg/BSF/NIT/CO W/2026-27][2026_BSF_912822_1]</t>
+          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>DG,BSF,MHA||Punjab Ftr(Jallundhar),BSF,MHA</t>
+          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3,18,03,649</t>
+          <t>1,34,50,000</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>31803649</v>
+        <v>13450000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST0y9WeppUHo6r4QjpFCucw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Captured Backup</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1256.</t>
+          <t>47.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24-Jun-2026 05:00 PM</t>
+          <t>15-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>16-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 11/2026-27 of EE M and Jodhpur][2026_MEDIC_570931_1]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1,67,51,919</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>16751919</v>
+        <v>50000000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SH1I9Tmt7tSMrYmTE2Aq0ow%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1186,49 +1186,49 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5552.</t>
+          <t>205.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>25-Jun-2026 06:15 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23-Jun-2026 02:00 PM</t>
+          <t>12-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25-Jun-2026 02:00 PM</t>
+          <t>13-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur (Civil, Sanitary, Joinery works)] [NIT No.03/2026-27 EE M and H DivBharatpur/][2026_MEDIC_571221_1]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>5,00,00,000</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>13450000</v>
+        <v>50000000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si%2FvDRgEcsjwlBatNiPx9XA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1248,32 +1248,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5059.</t>
+          <t>1297.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>23-Jun-2026 04:20 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>15-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>16-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Rate Contract for Electric Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur ] [NIT No.05/2026-27 EE M and H DivBharatpur/][2026_MEDIC_570559_1]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>Medical and Health||Chief Engineer</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Shv4Y3gc9rnanMu%2BlPBC1%2FA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1306,32 +1306,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5375.</t>
+          <t>4492.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>10-Jun-2026 04:50 PM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>25-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>Medical and Health</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1364,27 +1364,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5389.</t>
+          <t>4674.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04-Jun-2026 10:00 AM</t>
+          <t>04-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>29-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>30-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Sawai Madhopur (Civil, Sanitary, Joinery works)] [Nit No. 04/2026-27 Executive Engineer Medical and Health Sawai Madhopur][2026_MEDIC_564750_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sww%2B5SwrMryuSox7h9K39OQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1422,27 +1422,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5395.</t>
+          <t>4889.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04-Jun-2026 09:00 AM</t>
+          <t>08-May-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23-Jun-2026 06:00 PM</t>
+          <t>02-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>24-Jun-2026 11:00 AM</t>
+          <t>03-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 09/2026-27 of EE M and Jodhpur][2026_MEDIC_564531_1]</t>
+          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SS7B95%2BlKtxmHztYWSYQXkQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5641.</t>
+          <t>4618.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>08-Jun-2026 04:00 PM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>29-Jun-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>30-Jun-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1510,131 +1510,15 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>4,48,00,000</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>50000000</v>
+        <v>44800000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rajasthan eProcurement</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5286.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
           <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Captured Backup</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Central eProcure</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2078.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>03-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 06:05 PM</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>[Comprehensive Annual Repair Maintenance and Operations (ARMO) of ESIC Hospital and Staff Quarters at Kala Amb, Distt-Sirmour, HP- during 2026-27.] [W-17/1/2026/RO-PMD-Misc][2026_ESIC_911422_1]</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Employees State Insurance Corporation||R.O. Himachal Pradesh</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1,30,03,957</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>13003957</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc6oEKlA0tALrMKwrkHr0%2Fg%3D%3D</t>
         </is>
       </c>
     </row>

--- a/all_captured_1cr_tenders.xlsx
+++ b/all_captured_1cr_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,297 +481,297 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>134.</t>
+          <t>1697.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22-Jun-2026 04:15 PM</t>
+          <t>18-Jun-2026 10:45 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:00 PM</t>
+          <t>06-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06-Jul-2026 03:30 PM</t>
+          <t>07-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
+          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4,50,46,000</t>
+          <t>19,08,13,426</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>45046000</v>
+        <v>190813426</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uttarakhand eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>420.</t>
+          <t>1900.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-Jun-2026 04:15 PM</t>
+          <t>02-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30-Jun-2026 12:30 PM</t>
+          <t>15-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30-Jun-2026 01:00 PM</t>
+          <t>16-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of non-residential office building of Rural Works Department Division Rudraprayag in village Raitoli under district Rudraprayag.] [267/R.W.D/T.I-02/2026-27][2026_RES_96577_2]</t>
+          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RES - Chief Engineer||SE - Pauri||EE - Pauri</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2,91,40,100</t>
+          <t>9,61,59,224</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>29140100</v>
+        <v>96159224</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sr16X%2F03zxO9kqVRVCdU%2FXg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Uttarakhand eTenders</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>328.</t>
+          <t>261.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25-Jun-2026 03:15 PM</t>
+          <t>22-Jun-2026 04:15 PM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14-Jul-2026 04:00 PM</t>
+          <t>06-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15-Jul-2026 02:00 PM</t>
+          <t>06-Jul-2026 03:30 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2,81,43,000</t>
+          <t>4,50,46,000</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>28143000</v>
+        <v>45046000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>JK eTenders</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>82.</t>
+          <t>2118.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>25-Jun-2026 03:15 PM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>03-Jul-2026 06:00 PM</t>
+          <t>14-Jul-2026 04:00 PM</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>06-Jul-2026 11:00 AM</t>
+          <t>15-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
+          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1,59,20,000</t>
+          <t>2,81,43,000</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>15920000</v>
+        <v>28143000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Punjab eProcurement</t>
+          <t>Rajasthan eProcurement</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1325.</t>
+          <t>1766.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>26-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>03-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>06-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>1,59,20,000</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>11000000</v>
+        <v>15920000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -780,36 +780,36 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4863.</t>
+          <t>1548.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14-May-2026 06:00 PM</t>
+          <t>26-Jun-2026 05:05 PM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>01-Jul-2026 02:00 PM</t>
+          <t>03-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>03-Jul-2026 04:00 PM</t>
+          <t>06-Jul-2026 11:15 AM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[Const. of Division /Sub-Division office building (Vig) and Protection at Jalore] [Nit01/2026-27][2026_JdVVN_558872_11]</t>
+          <t>[Construction of sub division office building at Jalsu, Jaipur.] [E-NIT 02/2026-27][2026_JVVNL_571333_21]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>JVVNL - CMD||CE(O and M), Jaipur||SE-Civil</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -822,27 +822,27 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SNkhzU01BT2m0XCYhaGOUUQ%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SlitjipCXcMe89SOZqYq2oQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JK eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>193.</t>
+          <t>1097.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -852,158 +852,158 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>17-Jul-2026 04:00 PM</t>
+          <t>02-Jul-2026 12:00 PM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18-Jul-2026 12:00 PM</t>
+          <t>02-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
+          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>PWD||CE RandB Jammu</t>
+          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8,46,91,000</t>
+          <t>1,98,80,991</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>84691000</v>
+        <v>19880991</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Himachal eTenders</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>377.</t>
+          <t>1802.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23-Jun-2026 05:00 PM</t>
+          <t>12-Jun-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>03-Jul-2026 04:00 PM</t>
+          <t>03-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>04-Jul-2026 11:00 AM</t>
+          <t>03-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
+          <t>[Construction of EVM Warehouse Godown at Sector-2 Rohtak] [2026700D3E7D 53FE 43DE 9797 BE9913718D62653BAR][2026_HRY_528819_1]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Rohtak||EE PD-2 Rohtak</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6,07,83,682</t>
+          <t>10,51,01,701</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>60783682</v>
+        <v>105101701</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sry5YRZyJYErEnc0cX5iBww%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Review Tender</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rajasthan eProcurement</t>
+          <t>Haryana eTenders</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>683.</t>
+          <t>1540.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25-Jun-2026 09:00 AM</t>
+          <t>22-Jun-2026 05:00 PM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>15-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>06-Jul-2026 11:00 AM</t>
+          <t>16-Jul-2026 09:00 AM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
+          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1,39,27,000</t>
+          <t>9,55,97,065</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13927000</v>
+        <v>95597065</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1012,56 +1012,56 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>158.</t>
+          <t>2010.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:00 PM</t>
+          <t>01-May-2026 03:00 PM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>02-Jul-2026 12:00 PM</t>
+          <t>13-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>02-Jul-2026 02:00 PM</t>
+          <t>14-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
+          <t>Haryana Government||GJUS and T Hisar</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1,98,80,991</t>
+          <t>1,58,61,542</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>19880991</v>
+        <v>15861542</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1070,56 +1070,56 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4807.</t>
+          <t>295.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21-May-2026 05:00 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>01-Jul-2026 02:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>03-Jul-2026 02:00 PM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[Construction of Building and Boundary wall at 04 Nos 33 kv s/s at Bijariya Bawadi (under Tinwari S/D), Hanuman Sagar (under Chamu S/D), Hapasar (under Sekhala S/D), Sadul Nagar (under Chamu S/D) under Distt. Circle), Jodhpur] [NIT 01/26-27 JU][2026_JdVVN_561401_1]</t>
+          <t>[Construction of Police Station Building at Savina in district Udaipur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_4]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Jodhpur VVNL - MD||CE (HQ)||SE(CIVIL)||TA to SE(CIVIL), JODHPUR</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1,34,50,000</t>
+          <t>3,11,00,000</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>13450000</v>
+        <v>31100000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SKOJOYsCWuD7th2nNI3TIng%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLIOzXMySdAgtJmxjwwPIeA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1128,56 +1128,56 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.</t>
+          <t>294.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26-Jun-2026 09:00 AM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jodhpur (Civil, Sanitary, Joinery works)] [Nit No. 11/2026-27 of EE M and Jodhpur][2026_MEDIC_570931_1]</t>
+          <t>[Construction of Police station Building at Sadar Bazar under Police Commissionerate Jodhpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_3]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,10,24,000</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>50000000</v>
+        <v>31024000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SH1I9Tmt7tSMrYmTE2Aq0ow%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SR7Njsl%2FDbjyCmTu9Cl1t2g%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1186,56 +1186,56 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>205.</t>
+          <t>298.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25-Jun-2026 06:15 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>12-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur (Civil, Sanitary, Joinery works)] [NIT No.03/2026-27 EE M and H DivBharatpur/][2026_MEDIC_571221_1]</t>
+          <t>[Construction of Police station building at Obri Distt Dungarpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_5]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,06,80,000</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>50000000</v>
+        <v>30680000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si%2FvDRgEcsjwlBatNiPx9XA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SZsTEje51qysdt9eVkLvAaA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1244,56 +1244,56 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1297.</t>
+          <t>299.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23-Jun-2026 04:20 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[Rate Contract for Electric Repair and Maintenance work at Various Hospital Buildings under Jurisdiction of NHM Division Bharatpur ] [NIT No.05/2026-27 EE M and H DivBharatpur/][2026_MEDIC_570559_1]</t>
+          <t>[Construction of Police station building at Januthar Distt Deeg. ] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_6]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,05,74,000</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>50000000</v>
+        <v>30574000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Shv4Y3gc9rnanMu%2BlPBC1%2FA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SeiwOPN0Q9AfFa4q0d0HBcw%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1302,56 +1302,56 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4492.</t>
+          <t>300.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10-Jun-2026 04:50 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Kota. (Civil, Electric, Sanitary, Joinery works)] [EE M and H Kota NIT No. 04/2026-27][2026_MEDIC_565771_1]</t>
+          <t>[Construction of Police station Building at Chourashi in district Dungarpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_7]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Medical and Health</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>3,05,00,000</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>50000000</v>
+        <v>30500000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJlGBFf4g9fkxvXcsRC5fGA%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SAiilRqcj30%2BVXlFHowIJsQ%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1360,56 +1360,56 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4674.</t>
+          <t>301.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04-Jun-2026 05:05 PM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29-Jun-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30-Jun-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-II. (Civil, Sanitary, Joinery works)] [NIT No.05/2026-27EEM and HDiv 2 Jaipur/][2026_MEDIC_564977_1]</t>
+          <t>[Remaining work for construction of Police Station Building at Pahari Disttt. Bharatpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_8]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,76,65,000</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>50000000</v>
+        <v>17665000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHZR5G1CZ1n2laFIQysmK4g%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SivrN%2B%2BGQc4lszerKDwzJCA%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Captured Backup</t>
+          <t>Best Tender</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1418,107 +1418,2253 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4889.</t>
+          <t>302.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08-May-2026 09:00 AM</t>
+          <t>01-Jul-2026 02:00 PM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>02-Jul-2026 06:00 PM</t>
+          <t>22-Jul-2026 06:00 PM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>03-Jul-2026 11:00 AM</t>
+          <t>23-Jul-2026 01:00 PM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[Rate Contract for General Repair and Maintenance work at Various Hospital Buildings under jurisdiction of NHM Division Jaipur-I. (Civil, Sanitary, Joinery works)] [NIT 09 2026-27 divi jaipurI][2026_MEDIC_557384_1]</t>
+          <t>[Remaining work of Police station Building at Itawa in district Kota] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_9]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Medical and Health||Chief Engineer</t>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5,00,00,000</t>
+          <t>1,67,35,000</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>50000000</v>
+        <v>16735000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqdkfmioPRgMN%2BuVcWZkXJw%3D%3D</t>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SISTXtJy2gLusBA%2FoSCGfVg%3D%3D</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>46.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[Construction of Heliport at Rora Tehsil Haroli Distt.Una SH C/o Building portion, WS and SI, Safety tank, Rain water harvesting tank, Heliport, Site development, overhead tank, Hanger, watch Tower, Security hut and approach road, providing E.I. Fire ] [Job1 Construction of Heliport at Rora Tehsil Haroli Distt.Una SH C/o Building portion, WS and SI, Sa][2026_PWD_137756_1]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PWD</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14,39,13,728</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>143913728</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc1jGj5kxAFe9wiyhRytfLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Central eProcure</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>45</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1283.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>18-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>20-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[Major Civil Repairs Work at Administrative Block Building, AJNIFM Campus, Sector-48, Faridabad (Haryana)] [AJNIFM/Civil/2026-27/02][2026_DEXP_913889_1]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Department of Expenditure||National Institute of Financial Management,DoE,MoF||Administration-NIFM - DOE</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1,60,53,363</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>16053363</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://eprocure.gov.in/eprocure/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SqLIcR0oNNfX%2FttiKnGHdeQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Punjab eProcurement</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>836.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[Construction of Govt ITI Building G plus 5 Centre of Excellence at Nangal Distt Ropar ] [Tender Notice No. 9 Dated 19.06.2026][2026_CEPW_170505_1]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CE-PWD(B and R)||Construction Circle-Chandigarh||Construction Division-Ropar</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19,43,71,801</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>194371801</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6W2ferMHIsjtTQZh3GJ0wQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>40</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3898.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[Construction work for the Fire Station and Garage Wing of the Bundi Municipal Council.] [NPB/Nirman/2026-27/3144 Dated 05/06/2026][2026_DLB_567746_3]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>DLB||Dy.DR-Kota||Commissioner-Bundi</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>10,93,04,000</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>109304000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SOcbSjzEC3BXIQm3Q51hqtQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>40</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4187.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20-May-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[Neurovascular Intervention Implant for Neurosurgery Department] [1377_19.05.2026][2026_SMSMC_560591_1]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10,00,00,000</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SCH1R%2FLkR%2BnUKTAurOmciqg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3892.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>10-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[Construction of Govt. ITI Building (4 Trade) at Bardod, Distt. Kotputli-Behror] [RSAMB/Alwar/NIT-07/2026-27(1)][2026_RSAMB_567646_1]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Jaipur||Ex.En. - Alwar</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>7,43,29,000</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>74329000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMcp3WJpJVJkSxOx6W8N2gw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>25.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[MRI, CT Scan and X-ray films for Radiodiagnosis dept.] [06/2026-27][2026_GMCK_572227_1]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5,68,00,000</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>56800000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S5lOBWFRPRjKrz8WUhp%2B1Mw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>35</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1072.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[Mechanized Cleaning and Senitation Services] [mechanized cleaning and sanitation service ][2026_SNMCJ_571544_1]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Dr. S.N.Medical College, Jodhpur||Principal-and-Controller||Superintendent- Umed Hospital</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5,25,00,000</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>52500000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S18rI9ojqNkY1Cda93%2BNNpA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>35</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3051.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[Security Guard Skilled worker Tender for RNT Medical College and Attached Hospitals for One Year] [1387][2026_RNTMC_570234_2]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>RNT Medical College, Udaipur||Principal and Controller.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2BvYNLR0%2BmxX%2FgWsG0t4ZyA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>35</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1949.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[Miscellaneous Items for HPB and Liver Transplant Surgery OT] [1711_24.06.2026][2026_SMSMC_571079_1]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4,25,00,000</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SgnhV0AOaF30etap8FNepJA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>35</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>946.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>30-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>31-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[neurosurgery items consumable, proprietory,implants tender] [436][2026_GMCK_571795_1]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller||Superintendent, Super Speciality Hospital Kota</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>3,45,00,000</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>34500000</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SVY8L16B%2B9sz39EznSAOBBA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>35</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>293.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[Construction of administratve block of Police Station Aakola at Distt. Chittorgarh] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_2]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>3,16,40,000</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>31640000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMXLsU4fDnpy8pNfYftL3Kw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>35</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4156.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>29-May-2026 05:30 PM</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[Construction Work of Library and Co-Working Station Building in Sawai Madhopur] [E-NIT No. 04/2026-27 UIT Sawai Madhopur ][2026_UITSM_563395_1]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>UIT - SAWAI MADHOPUR||SECRETARY||EXECUTIVE ENGINEER</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3,00,00,000</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sh38dQxKdtdyvKhLKMX7nAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>35</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2902.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[BALANCE WORK FOR CONSTRUCTION OF NEW PAVILLION BUILDING AND OTHER ALLIED WORKS AT SUBASH STADIUM UDHMAPUR 2nd time ] [e nit 12 of 2026-27 dated 20.06.2026][2026_SPORT_313266_1]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>J and K State Sports Council||Sports Council Construction Div Jammu</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2,92,74,000</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>29274000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S9jWeTiz91AXTipQZplL8vg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Uttarakhand eTenders</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>35</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>214.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[Construction work of restaurant and community centre under Vibrant Village in village Rongkong of development block Dharchula] [329 DATED 23-06-2026][2026_RES_96930_1]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>RES - Chief Engineer||SE - Pithoragarh</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2,84,90,000</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>28490000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScuXPTCf2qgSeP5Ho2OAWPQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>35</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>964.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>27-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>28-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[KITCHEN AND DIETARY SERVICES] [MCGMC/E-TENDER/2026/0003][2026_HRY_531897_1]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Maharishi Chyawan Medical College Koriawas Narnaul</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2,50,00,000</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SrJ9LRlgIfIaDXDKDCQLj5Q%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>35</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1300.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 05:50 PM</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[Library Books] [MCGMC/E-TENDER/2026/0001][2026_HRY_531408_1]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Maharishi Chyawan Medical College Koriawas Narnaul</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2,50,00,000</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SyW7Kri2R3OCjLewhnCvr4w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>35</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4199.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>15-May-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[Surgical And Suture Items Tender] [212][2026_GMCK_559661_1]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Govt. Medical College, Kota||Principal and Controller||Superintendent, Super Speciality Hospital Kota</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2,12,00,000</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>21200000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ScbrvXhGmoKQgtGAXfYxdKA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>35</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1388.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[Rough Cost Estimate for Various Construction works in Community Centre Sector-46 Ward No.20, Faridabad.] [202695CC0C9C FA7A 4968 BE73 7681F457F169284ULB][2026_HRY_531268_1]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Haryana Government||Urban Local Bodies||Faridabad</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1,93,54,683</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>19354683</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SloPzjrH0560YEBA7BHgYpA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>35</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2183.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[Dismantling and reconstruction of food store building at Hiranagar.] [e-NIT No.PWD/SE/KS/17 of 2026-27 Dated 22-06-2026][2026_PWDJK_313596_1]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1,71,91,000</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>17191000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SV0hDtoZc4nr5h8jv1EdsVw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>35</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1155.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[Service Contract] [PT/NRS/BH/14A][2026_HRY_531744_1]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Haryana Government||Directorate of Medical Education and Research||Pt. Nekiram Sharma Govt. Medical College Bhiwani</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1,60,00,000</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Si36wYGtipFe0hiuYvqSHPA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>35</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2256.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[Construction of New PHC Building at Burja (Block Malakhera) Distt. Alwar] [NIT NO. 07/2026-27(21)eemhalwar][2026_MEDIC_570999_1]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Medical and Health||Chief Engineer</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1,40,00,000</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SyQosoh%2FL1WEJUv%2FKgXTnAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>35</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>471.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>27-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[Construction of Sub-Tehsil Building at Majheen, Distt.Kangra(H.P)] [1514-15 dated 0206.2026][2026_PWD_137564_1]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PWD</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1,12,64,584</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>11264584</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SCGn9fBlgLprVNPXsoOHr6w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>35</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1050.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[Miscellaneous balance civil works of Plant and Non plant buildings at SSCTPS Suratgarh] [TN/STPS-SC/2026-27/290(Civil)][2026_RRVUN_570745_1]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>RRVUN - CMD||RVUN-CE (STPS-SC) SURATGARH</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1,10,71,370</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>11071370</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SospqnumSIEQgOinMxutOlQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>35</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3068.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[4k ICG Laparoscopic Endovision System] [1382][2026_RNTMC_570127_1]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RNT Medical College, Udaipur||Principal and Controller.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1,00,00,000</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S0kcBOnrt7Ree4DBm7tOGng%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>32</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1994.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>17-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>18-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[Construction of School Education Excellence Education Hub Samagra Office at Gandhi Nagar Jammu] [e-NIT No.08 of 2026-27 Dated 25.06.2026][2026_PWDJK_313690_1]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>8,46,91,000</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>84691000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLq3%2Fw%2BTEkXaa4HZKM1MTHQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>32</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>691.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>04-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[Construction of Auditorium Multipurpose Hall at Rajiv Gandhi Government Engineering College Kangra at Nagrota Bagwan District kangra HP including internal and external services] [HIMUDA/DD/2025-2956-65][2026_HIMUD_137323_1]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Himachal Urban Development Authority||Supdt. Engineer (N),HIMUDA||Executive Engineer Division,Dharamsala,HIMUDA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6,07,83,682</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>60783682</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SRIsC%2FuwYG9l9xB%2BpZpt6fw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>32</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>34.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[Construction of residences for Judicial Officers in Judicial Court Complex at Sector 27, Pinjore in District- Panchkula] [2026AA86EF83 87EC 456A B50B E053BF193A04619BAR][2026_HRY_532891_1]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE NH Panchkula</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4,93,28,386</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>49328386</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SUWmDcRlY6pUHY55gbdhOMA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>32</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2248.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[Construction of Shed (Size 130ftx50ft) for grading cleaning unit in main mandi yard Under KUMS Baran] [Nit No. 05/2026 SE RSAMB Circle Kota][2026_RSAMB_570944_1]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle Kota||Ex.En. - Kota</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1,39,27,000</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>13927000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SHPcldJwk8oyDteuMIUaPOw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Captured Backup</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Rajasthan eProcurement</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4618.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>08-Jun-2026 04:00 PM</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>29-Jun-2026 06:00 PM</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>30-Jun-2026 01:00 PM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>[Rate contract for General Repair and Maintenance Work at Various Hospital Buildings under jurisdiction of NHM Division Alwar (Annual Rate Contract)] [NIT NO. 05/2026-27(01)eemhalwar][2026_MEDIC_565647_1]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Medical and Health||Chief Engineer</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>4,48,00,000</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>44800000</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SslGsXAjXeu8uEKohFD43uQ%3D%3D</t>
+      <c r="C48" t="n">
+        <v>25</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3277.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>24-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>25-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[Tender for the Procurement of Fully Automated immunodiagnostic system based on latest chemiluminesnce techniques on Reagents Rental Method] [1540_08.06.2026][2026_SMSMC_569861_1]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller||SMS Hospital Jaipur</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>11,00,00,000</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SMx%2BQuPJrlNv%2FkvBqo5PTXg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>20</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1224.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[Construction of Community Centre on Bas-Bhangrola road in village Bhangrola in ward 06 under MC Manesar limit] [202614D22CA0 5C7D 4D88 AB43 52FC317DBA7B1809ULB][2026_HRY_531736_1]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Haryana Government||Urban Local Bodies||MC Manesar</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>7,68,83,803</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>76883803</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sq8qQOlcAQqZnmVMKtZjagw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>4228.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>17-Apr-2026 12:30 PM</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[Procurement of Gauge and Bandage for 02 years] [ENIB No 04 (2026-27)][2026_SPMCB_552196_1]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>S.P. Medical college, Bikaner||Principal, S.P.M.C., Bikaner||PBM A.G. HOSPITALS||SUPERINTENDENT</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Syw4F6SBZFGttK1HzsqKdgA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>20</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>101.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 05:30 PM</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>05-Aug-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>07-Aug-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[Setting up of ASU and Supply of Medical oxygen] [E-tender of Air Separation Unit ][2026_DMER5_137839_1]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Directorate of Medical Education and Research||Dr Rajendra Prasad Govt Medical College Tanda Kangra</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>5,00,00,000</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S5cZtX41mGcgxuk1aO1fnGg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>20</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3919.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>01-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>11-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[DESIGN, SUPPLY, INSTALLATION, TESTING, COMMISSIONING OF HVAC SYSTEM AT TEACHING HOSPITAL, GOVERNMENT MEDICAL COLLEGE DODA] [e- NIT No.MHCJ/Tech/e-NIT/2026-27/04 ][2026_PWDJK_311243_1]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>PWD||CE MED Jammu||Mechanical Circle Jammu</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>4,97,94,781</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>49794781</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Slx9M53hmIEhkOsQJDIct2w%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3308.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[Purchase of desktop computer] [17/2267-73 Dated- 16/06/2026][2026_SMSMC_569061_1]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1,96,59,000</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>19659000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SnCYS0i0gD4QMesbx3OsNAw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>20</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>868.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[Const. of the building Mother and Child Block at Civil Hospital at Sonipat (Pdg. 01 No. 13 Passenger, 04 No. Bed Lift and 01 No. Dumbwaiter Lift). Recall] [202666510592 F004 436F ABE8 2656471BFB6E665BAR][2026_HRY_532088_1]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE (Elect.) Karnal||EE Elect. Karnal</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1,58,60,000</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>15860000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SXqMf39QjSypa7kfuDJeRgA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>20</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3320.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20-Jun-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[Purchase of Echo machine with TEE machine for CTVS department] [28/2267-73 Dated- 16/06/2026][2026_SMSMC_569513_1]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>S.M.S. Medical College-Jaipur||Principal and Controller</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1,55,00,000</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>15500000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SDNIOm79HSPSzlXWxxPk90g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Captured Backup</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>20</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2516.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>24-Jun-2026 10:00 AM</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>09-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[Package 01/2026-27/Construction of Various Development works/Bus stand Building/CC Road/Toilet Block at RSRTC Hanumangarh Depot Distt Hanumangarh. ] [EE-RSAMB-HMH-NIT-06-2026-27][2026_RSAMB_570289_1]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone II||S.E. - Circle SGNR||Ex.En. - Sriganganagar</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1,36,37,000</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>13637000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Svv%2BeP0mqARZt1Jkx%2BRZgig%3D%3D</t>
         </is>
       </c>
     </row>
